--- a/data/trans_bre/P20B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 9,9</t>
+          <t>-40,19; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 22,85</t>
+          <t>-29,91; 23,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,23; -6,48</t>
+          <t>-50,86; -6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,08; -14,04</t>
+          <t>-51,64; -13,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,89; 119,31</t>
+          <t>-88,1; 67,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,04; 173,55</t>
+          <t>-73,96; 197,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,57</t>
+          <t>-100,0; 17,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,7; -41,47</t>
+          <t>-90,84; -29,84</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 15,07</t>
+          <t>-29,89; 15,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 19,34</t>
+          <t>-15,12; 20,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 28,4</t>
+          <t>-18,32; 28,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 20,96</t>
+          <t>-29,92; 17,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 518,16</t>
+          <t>-63,47; 439,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 126,82</t>
+          <t>-64,5; 97,64</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 12,79</t>
+          <t>-50,83; 6,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 22,13</t>
+          <t>-25,54; 20,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 40,91</t>
+          <t>-22,66; 41,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 8,69</t>
+          <t>-41,88; 9,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,84; 69,7</t>
+          <t>-100,0; 50,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 96,22</t>
+          <t>-66,66; 96,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 190,81</t>
+          <t>-55,2; 182,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,7; 26,5</t>
+          <t>-77,33; 23,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 13,74</t>
+          <t>-16,44; 10,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 2,44</t>
+          <t>-26,12; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,64; -4,72</t>
+          <t>-39,48; -4,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 5,54</t>
+          <t>-21,05; 5,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 98,83</t>
+          <t>-57,03; 75,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 11,62</t>
+          <t>-68,66; 8,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,04; -12,64</t>
+          <t>-75,07; -11,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,3; 33,19</t>
+          <t>-65,96; 34,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 17,38</t>
+          <t>-37,37; 15,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 18,36</t>
+          <t>-19,0; 19,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 26,49</t>
+          <t>-22,17; 29,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 17,39</t>
+          <t>-19,56; 17,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 215,16</t>
+          <t>-74,12; 123,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 82,82</t>
+          <t>-39,32; 88,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 127,46</t>
+          <t>-43,5; 157,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 85,16</t>
+          <t>-45,94; 79,43</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 30,56</t>
+          <t>-77,22; 29,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 15,99</t>
+          <t>-51,95; 18,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 25,65</t>
+          <t>-30,25; 26,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,03; 34,88</t>
+          <t>-60,28; 34,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,39; 144,96</t>
+          <t>-70,41; 160,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 1,92</t>
+          <t>-14,9; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 2,45</t>
+          <t>-13,18; 3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 0,05</t>
+          <t>-18,99; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,3; -1,24</t>
+          <t>-18,89; -2,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 10,86</t>
+          <t>-47,18; 13,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 10,88</t>
+          <t>-38,42; 13,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 0,31</t>
+          <t>-48,1; 2,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,1; -4,06</t>
+          <t>-50,17; -8,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-32,62</t>
+          <t>-32,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-76,2%</t>
+          <t>-75,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 7,47</t>
+          <t>-41,18; 9,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 23,12</t>
+          <t>-32,37; 22,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-50,86; -6,73</t>
+          <t>-52,61; -7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -13,03</t>
+          <t>-53,91; -13,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 67,68</t>
+          <t>-90,38; 89,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 197,24</t>
+          <t>-72,49; 224,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,44</t>
+          <t>-100,0; 6,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,84; -29,84</t>
+          <t>-92,49; -39,72</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,61%</t>
+          <t>-10,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 15,89</t>
+          <t>-32,97; 15,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 20,91</t>
+          <t>-18,85; 19,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 28,13</t>
+          <t>-19,3; 28,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 17,29</t>
+          <t>-26,91; 19,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-90,8; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 439,75</t>
+          <t>-60,96; 481,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 97,64</t>
+          <t>-57,31; 110,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-17,45</t>
+          <t>-22,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,6%</t>
+          <t>-46,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 6,79</t>
+          <t>-46,5; 10,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 20,92</t>
+          <t>-26,11; 20,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 41,1</t>
+          <t>-25,81; 41,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 9,55</t>
+          <t>-46,64; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,11</t>
+          <t>-90,74; 67,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 96,19</t>
+          <t>-69,36; 102,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 182,11</t>
+          <t>-57,64; 187,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 23,39</t>
+          <t>-82,76; 6,98</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-5,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-28,62%</t>
+          <t>-23,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 10,84</t>
+          <t>-16,41; 11,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 1,67</t>
+          <t>-26,49; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -4,4</t>
+          <t>-36,93; -1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 5,74</t>
+          <t>-18,37; 6,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 75,87</t>
+          <t>-57,93; 78,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 8,43</t>
+          <t>-67,42; 13,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,07; -11,16</t>
+          <t>-72,4; -0,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 34,02</t>
+          <t>-61,68; 43,28</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 15,78</t>
+          <t>-33,08; 17,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 19,02</t>
+          <t>-19,43; 18,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 29,44</t>
+          <t>-23,66; 25,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 17,55</t>
+          <t>-16,63; 21,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 123,29</t>
+          <t>-71,49; 155,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 88,09</t>
+          <t>-39,28; 86,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 157,12</t>
+          <t>-44,06; 117,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 79,43</t>
+          <t>-39,71; 107,94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,41</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>101,89%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,22; 29,79</t>
+          <t>-74,82; 30,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,95; 18,64</t>
+          <t>-53,11; 17,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 26,34</t>
+          <t>-28,09; 26,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 34,19</t>
+          <t>-34,21; 35,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 160,44</t>
+          <t>-74,95; 140,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-10,49</t>
+          <t>-10,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-31,55%</t>
+          <t>-30,65%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,69</t>
+          <t>-14,99; 2,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 3,48</t>
+          <t>-13,53; 2,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 0,61</t>
+          <t>-18,67; -0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -2,76</t>
+          <t>-17,84; -1,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 13,67</t>
+          <t>-47,19; 14,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 13,89</t>
+          <t>-38,3; 10,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 2,99</t>
+          <t>-46,47; -0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,17; -8,21</t>
+          <t>-48,01; -5,98</t>
         </is>
       </c>
     </row>
